--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260607_210139.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
